--- a/test_data/WTA/Treaties OtherArticles/Treaties OtherArticles_Test_Cases.xlsx
+++ b/test_data/WTA/Treaties OtherArticles/Treaties OtherArticles_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Other Articles loaded correctly at https://regplus.reganalytics.com/wta/OtherArticles.</t>
+          <t>Other Articles loaded correctly at https://regplus.kaz.com.bd/wta/OtherArticles.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered the Other Articles table with the expected headers and 45 rows.</t>
+          <t>Selecting Australia rendered the Other Articles table with the expected headers and 43 rows.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -629,35 +629,512 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>OtherArticles_03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>The Austria row shows the expected Tie Breaker Corporate article</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, the row for 'Austria' must show 'Art. 4(4)' as its Tie Breaker Corporate article reference.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Australia
+3. Verify the 'Austria' row contains 'Art. 4(4)'</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, the row for 'Austria' must show 'Art. 4(4)' as its Tie Breaker Corporate article reference.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>The 'Austria' row correctly shows 'Art. 4(4)' as its Tie Breaker Corporate article reference.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The 'Austria' row contains 'Art. 4(4)'</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Switching the 'MEA' region tab changes the visible country list</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'MEA' region tab must change the visible jurisdiction list away from the default Asia Pacific set - confirmed by 'Australia' no longer being visible.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Region: MEA</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Click the 'MEA' region tab
+3. Verify 'Australia' is no longer visible</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the 'MEA' region tab must change the visible jurisdiction list away from the default Asia Pacific set - confirmed by 'Australia' no longer being visible.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Switching to the 'MEA' region tab correctly changed the jurisdiction list away from Asia Pacific ('Australia' no longer visible).</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'Australia' is not visible under the MEA region tab</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent country shows the 'No countries found' message</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Search text: zzzznotarealcountry</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Type 'zzzznotarealcountry' into the search box
+3. Verify the 'No countries found' message is shown</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Searching for a non-existent country correctly showed the 'No countries found' message.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No countries found matching...' message is shown for an unmatched search</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking an article-reference link opens the treaty article modal</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the 'Art. 4(4)' link in the Austria row's 'Tie Breaker Corporate' column must open a modal titled 'Treaty between Australia and Austria' showing the Article 4(4) text.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria, column: Tie Breaker Corporate</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Australia
+3. Click the 'Art. 4(4)' link in the Austria row
+4. Verify the article modal title and content</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the 'Art. 4(4)' link in the Austria row's 'Tie Breaker Corporate' column must open a modal titled 'Treaty between Australia and Austria' showing the Article 4(4) text.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Austria article link correctly opened the modal ('Treaty between Australia and Austria\nFull DTA').</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The article modal opens with the correct treaty title and article text</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's PDF export downloads a real, non-empty file</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click 'PDF' under Export
+4. Verify a real, non-empty PDF download completed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>PDF export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.pdf' (17727 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The PDF export downloads a real, non-empty .pdf file with no failure</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's Word export downloads a real, non-empty file</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'Word' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click 'Word' under Export
+4. Verify a real, non-empty Word download completed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'Word' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Word export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.doc' (8364 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The Word export downloads a real, non-empty .doc(x) file with no failure</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's Print action opens a print-preview tab with the expected content</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'Print' under Export must open a NEW browser tab showing a print-preview rendering of the treaty name and article text. The test verifies the preview content and closes the tab - it never clicks any actual 'Print' confirmation control.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click 'Print' under Export
+4. Verify the new print-preview tab shows the treaty name and article text, then close it</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'Print' under Export must open a NEW browser tab showing a print-preview rendering of the treaty name and article text. The test verifies the preview content and closes the tab - it never clicks any actual 'Print' confirmation control.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>The Print action correctly opened a print-preview tab with the expected treaty/article content (no Print confirmation control was clicked).</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The print-preview tab shows the treaty name and Article 4(4) text</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's 'Full DTA' link swaps in the full document viewer</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking the 'Full DTA' link in the modal header must swap the modal's content for the full DTA document viewer - a 'Contents' sidebar listing every treaty article.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Other Articles, select Australia
+2. Open the Austria article modal
+3. Click the 'Full DTA' link
+4. Verify the 'Contents' sidebar with article entries is shown</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking the 'Full DTA' link in the modal header must swap the modal's content for the full DTA document viewer - a 'Contents' sidebar listing every treaty article.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>The 'Full DTA' link correctly opened the full document viewer (32 article entries).</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The 'Full DTA' link swaps in the full document viewer with a populated Contents sidebar</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>OtherArticles_11</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>The article modal's header X button closes it</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking the header X close button must dismiss the modal.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's article modal open.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Other Articles, select Australia
 2. Open the Austria article modal
@@ -665,59 +1142,59 @@
 4. Verify the modal is no longer visible</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking the header X close button must dismiss the modal.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>The header X button correctly closed the article modal.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>[PASS] The article modal is no longer visible after clicking the X close button</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_12</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>The table-level 'Export as Excel' button downloads the whole table</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on Other Articles.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Select Australia
@@ -725,59 +1202,179 @@
 4. Verify a real, non-empty .xlsx download completed</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Table export downloaded 'AU_OtherArticles.xlsx' (4347 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Table export downloaded 'AU_OtherArticles.xlsx' (4290 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>[PASS] Exporting the table downloads a real, non-empty .xlsx file with no failure</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Article link + PDF export work correctly for a second country (Canada)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>With Canada selected, clicking the Algeria row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior is not Australia-specific.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Country: Canada, partner: Algeria</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Canada
+3. Click the Algeria row's article link and verify the modal title
+4. Click 'PDF' under Export and verify a real download</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>With Canada selected, clicking the Algeria row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior is not Australia-specific.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Canada's article link/modal/PDF export all worked correctly ('CA_DZ_Art. 4(3)_Treaty_Article.pdf', 18287 bytes).</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Canada's article modal and PDF export both work correctly</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>OtherArticles_14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Treaties OtherArticles</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Article link + PDF export work correctly for a third country (Germany)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>With Germany selected, clicking the Albania row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior generalizes across countries.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Other Articles.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Country: Germany, partner: Albania</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Other Articles
+2. Select Germany
+3. Click the Albania row's article link and verify the modal title
+4. Click 'PDF' under Export and verify a real download</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>With Germany selected, clicking the Albania row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior generalizes across countries.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Germany's article link/modal/PDF export all worked correctly ('DE_AL_Art. 4 (3)_Treaty_Article.pdf', 17979 bytes).</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Germany's article modal and PDF export both work correctly</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_15</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>A cell with no treaty article coverage ('None') has no clickable link</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, Belgium's 'Other Income' cell shows plain 'None' text with no linked article - clicking it must not open any modal. This is the genuine negative case for the article-link feature.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on Other Articles.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Belgium, column: Other Income</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Select Australia
@@ -785,22 +1382,22 @@
 4. Verify no article modal opens</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, Belgium's 'Other Income' cell shows plain 'None' text with no linked article - clicking it must not open any modal. This is the genuine negative case for the article-link feature.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Belgium's 'Other Income' cell correctly shows plain 'None' text with no clickable article link (genuine no-coverage case).</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>[PASS] Belgium's 'Other Income' cell shows plain 'None' text with no clickable article link</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/Treaties OtherArticles/Treaties OtherArticles_Test_Cases.xlsx
+++ b/test_data/WTA/Treaties OtherArticles/Treaties OtherArticles_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>OtherArticles_01</t>
+          <t>OtherArticles_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,319 +522,202 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Other Articles page loads with the jurisdiction panel</t>
+          <t>The Austria row shows the expected Tie Breaker Corporate article</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load at /wta/OtherArticles with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
+          <t>With Australia selected, the row for 'Austria' must show 'Art. 4(4)' as its Tie Breaker Corporate article reference.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia selected on Other Articles.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Other Articles
-2. Verify URL, heading and placeholder text</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>The page must load at /wta/OtherArticles with the 'Select Jurisdiction' heading and the left-panel placeholder text visible before any country is selected.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Other Articles loaded correctly at https://regplus.kaz.com.bd/wta/OtherArticles.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Other Articles loads with URL/heading/placeholder all present</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>OtherArticles_02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Treaties OtherArticles</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting a jurisdiction renders the Other Articles table</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' must render a table with columns ['Jurisdiction', 'Tie Breaker Corporate', 'Capital Gain', 'Other Income', 'Exchange of Information'] and multiple rows.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Other Articles.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Other Articles
-2. Select Australia
-3. Verify the table headers and row count</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' must render a table with columns ['Jurisdiction', 'Tie Breaker Corporate', 'Capital Gain', 'Other Income', 'Exchange of Information'] and multiple rows.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia rendered the Other Articles table with the expected headers and 43 rows.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Other Articles table shows the expected columns and at least one row</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>OtherArticles_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Treaties OtherArticles</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The Austria row shows the expected Tie Breaker Corporate article</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, the row for 'Austria' must show 'Art. 4(4)' as its Tie Breaker Corporate article reference.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Other Articles.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Select Australia
 3. Verify the 'Austria' row contains 'Art. 4(4)'</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, the row for 'Austria' must show 'Art. 4(4)' as its Tie Breaker Corporate article reference.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>The 'Austria' row correctly shows 'Art. 4(4)' as its Tie Breaker Corporate article reference.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>[PASS] The 'Austria' row contains 'Art. 4(4)'</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_04</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Switching the 'MEA' region tab changes the visible country list</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'MEA' region tab must change the visible jurisdiction list away from the default Asia Pacific set - confirmed by 'Australia' no longer being visible.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Other Articles.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Region: MEA</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Click the 'MEA' region tab
 3. Verify 'Australia' is no longer visible</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Clicking the 'MEA' region tab must change the visible jurisdiction list away from the default Asia Pacific set - confirmed by 'Australia' no longer being visible.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Switching to the 'MEA' region tab correctly changed the jurisdiction list away from Asia Pacific ('Australia' no longer visible).</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Australia' is not visible under the MEA region tab</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_05</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent country shows the 'No countries found' message</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Other Articles.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Search text: zzzznotarealcountry</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Type 'zzzznotarealcountry' into the search box
 3. Verify the 'No countries found' message is shown</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent country correctly showed the 'No countries found' message.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'No countries found matching...' message is shown for an unmatched search</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_06</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Clicking an article-reference link opens the treaty article modal</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, clicking the 'Art. 4(4)' link in the Austria row's 'Tie Breaker Corporate' column must open a modal titled 'Treaty between Australia and Austria' showing the Article 4(4) text.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on Other Articles.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria, column: Tie Breaker Corporate</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Select Australia
@@ -842,59 +725,59 @@
 4. Verify the article modal title and content</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, clicking the 'Art. 4(4)' link in the Austria row's 'Tie Breaker Corporate' column must open a modal titled 'Treaty between Australia and Austria' showing the Article 4(4) text.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Clicking the Austria article link correctly opened the modal ('Treaty between Australia and Austria\nFull DTA').</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] The article modal opens with the correct treaty title and article text</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_07</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>The article modal's PDF export downloads a real, non-empty file</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's article modal open.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Other Articles, select Australia
 2. Open the Austria article modal
@@ -902,59 +785,59 @@
 4. Verify a real, non-empty PDF download completed</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>PDF export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.pdf' (17727 bytes) successfully.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>[PASS] The PDF export downloads a real, non-empty .pdf file with no failure</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_08</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>The article modal's Word export downloads a real, non-empty file</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking 'Word' under Export must trigger a real file download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's article modal open.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Other Articles, select Australia
 2. Open the Austria article modal
@@ -962,59 +845,59 @@
 4. Verify a real, non-empty Word download completed</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking 'Word' under Export must trigger a real file download with no failure and a non-zero size.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Word export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.doc' (8364 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Word export downloaded 'AU_AT_Art. 4(4)_Treaty_Article.doc' (8363 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] The Word export downloads a real, non-empty .doc(x) file with no failure</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_09</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>The article modal's Print action opens a print-preview tab with the expected content</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking 'Print' under Export must open a NEW browser tab showing a print-preview rendering of the treaty name and article text. The test verifies the preview content and closes the tab - it never clicks any actual 'Print' confirmation control.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's article modal open.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Other Articles, select Australia
 2. Open the Austria article modal
@@ -1022,59 +905,59 @@
 4. Verify the new print-preview tab shows the treaty name and article text, then close it</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking 'Print' under Export must open a NEW browser tab showing a print-preview rendering of the treaty name and article text. The test verifies the preview content and closes the tab - it never clicks any actual 'Print' confirmation control.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>The Print action correctly opened a print-preview tab with the expected treaty/article content (no Print confirmation control was clicked).</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] The print-preview tab shows the treaty name and Article 4(4) text</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_10</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>The article modal's 'Full DTA' link swaps in the full document viewer</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking the 'Full DTA' link in the modal header must swap the modal's content for the full DTA document viewer - a 'Contents' sidebar listing every treaty article.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's article modal open.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Other Articles, select Australia
 2. Open the Austria article modal
@@ -1082,59 +965,59 @@
 4. Verify the 'Contents' sidebar with article entries is shown</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking the 'Full DTA' link in the modal header must swap the modal's content for the full DTA document viewer - a 'Contents' sidebar listing every treaty article.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>The 'Full DTA' link correctly opened the full document viewer (32 article entries).</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>The 'Full DTA' link correctly opened the full document viewer (29 article entries).</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>[PASS] The 'Full DTA' link swaps in the full document viewer with a populated Contents sidebar</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_11</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>The article modal's header X button closes it</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking the header X close button must dismiss the modal.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected, Austria's article modal open.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Austria</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Other Articles, select Australia
 2. Open the Austria article modal
@@ -1142,59 +1025,59 @@
 4. Verify the modal is no longer visible</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>With the Austria article modal open (Australia selected), clicking the header X close button must dismiss the modal.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>The header X button correctly closed the article modal.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>[PASS] The article modal is no longer visible after clicking the X close button</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_12</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>The table-level 'Export as Excel' button downloads the whole table</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on Other Articles.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Select Australia
@@ -1202,59 +1085,59 @@
 4. Verify a real, non-empty .xlsx download completed</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>With Australia selected (no article link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Table export downloaded 'AU_OtherArticles.xlsx' (4290 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Table export downloaded 'AU_OtherArticles.xlsx' (4347 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>[PASS] Exporting the table downloads a real, non-empty .xlsx file with no failure</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_13</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Article link + PDF export work correctly for a second country (Canada)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>With Canada selected, clicking the Algeria row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior is not Australia-specific.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Other Articles.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Country: Canada, partner: Algeria</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Select Canada
@@ -1262,59 +1145,59 @@
 4. Click 'PDF' under Export and verify a real download</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>With Canada selected, clicking the Algeria row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior is not Australia-specific.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Canada's article link/modal/PDF export all worked correctly ('CA_DZ_Art. 4(3)_Treaty_Article.pdf', 18287 bytes).</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>[PASS] Canada's article modal and PDF export both work correctly</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_14</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Article link + PDF export work correctly for a third country (Germany)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>With Germany selected, clicking the Albania row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior generalizes across countries.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Other Articles.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Country: Germany, partner: Albania</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Select Germany
@@ -1322,59 +1205,59 @@
 4. Click 'PDF' under Export and verify a real download</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>With Germany selected, clicking the Albania row's Tie Breaker Corporate article link must open the correctly-titled modal, and its PDF export must download a real, non-empty file - confirming the behavior generalizes across countries.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Germany's article link/modal/PDF export all worked correctly ('DE_AL_Art. 4 (3)_Treaty_Article.pdf', 17979 bytes).</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>[PASS] Germany's article modal and PDF export both work correctly</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>OtherArticles_15</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Treaties OtherArticles</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>A cell with no treaty article coverage ('None') has no clickable link</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, Belgium's 'Other Income' cell shows plain 'None' text with no linked article - clicking it must not open any modal. This is the genuine negative case for the article-link feature.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on Other Articles.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Country: Australia, partner: Belgium, column: Other Income</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Other Articles
 2. Select Australia
@@ -1382,22 +1265,22 @@
 4. Verify no article modal opens</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>With Australia selected, Belgium's 'Other Income' cell shows plain 'None' text with no linked article - clicking it must not open any modal. This is the genuine negative case for the article-link feature.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Belgium's 'Other Income' cell correctly shows plain 'None' text with no clickable article link (genuine no-coverage case).</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>[PASS] Belgium's 'Other Income' cell shows plain 'None' text with no clickable article link</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
